--- a/diseases/d157/2026-2029.xlsx
+++ b/diseases/d157/2026-2029.xlsx
@@ -11716,12 +11716,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -11746,22 +11746,22 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>0.4485542605576006</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT58" t="n">
@@ -11808,42 +11808,42 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -11875,12 +11875,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -11905,38 +11905,38 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Syst. gr. A streptokokksykdom</t>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -11996,17 +11996,17 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT59" t="n">
@@ -12042,40 +12042,433 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
+        <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW59" t="inlineStr">
+      <c r="AW60" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
+      <c r="AX60" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY59" t="inlineStr">
+      <c r="AY60" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
+      <c r="AZ60" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA59" t="inlineStr">
+      <c r="BA60" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB59" t="inlineStr">
+      <c r="BB60" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC59" t="inlineStr">
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN61" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP61" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV61" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA61" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB61" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC61" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -12197,7 +12590,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -12207,7 +12600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
@@ -12227,7 +12620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -12259,7 +12652,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1740</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d157/2026-2029.xlsx
+++ b/diseases/d157/2026-2029.xlsx
@@ -12148,13 +12148,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -12307,10 +12307,10 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1788</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d157/2026-2029.xlsx
+++ b/diseases/d157/2026-2029.xlsx
@@ -10144,12 +10144,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -10183,22 +10183,19 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="O50" t="n">
-        <v>17</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0.3007258903852361</v>
+        <v>93</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -10223,7 +10220,7 @@
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="AT50" t="n">
@@ -10236,42 +10233,42 @@
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10300,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -10342,29 +10339,29 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="O51" t="n">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Syst. gr. A streptokokksykdom</t>
+          <t>Group A Streptococcal Disease, Invasive</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -10374,7 +10371,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -10389,7 +10386,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
@@ -10424,17 +10421,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+          <t>Ontario IDTO current-year preliminary invasive group A streptococcal disease notifications.</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10457,7 +10454,7 @@
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="AT51" t="n">
@@ -10470,42 +10467,42 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10537,12 +10534,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -10576,13 +10573,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="O52" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="R52" t="n">
-        <v>1.134756279883097</v>
+        <v>0.3007258903852361</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -10591,7 +10588,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -10616,7 +10613,7 @@
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="AT52" t="n">
@@ -10629,42 +10626,42 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10693,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -10735,29 +10732,29 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="O53" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Invasive group A streptococcal infection</t>
+          <t>Syst. gr. A streptokokksykdom</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -10767,7 +10764,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -10782,7 +10779,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
@@ -10817,17 +10814,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly invasive group A streptococcal infection notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -10850,7 +10847,7 @@
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="AT53" t="n">
@@ -10863,42 +10860,42 @@
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -10930,12 +10927,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -10969,13 +10966,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="O54" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="R54" t="n">
-        <v>0.3270708149899171</v>
+        <v>1.134756279883097</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -10984,7 +10981,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -11009,7 +11006,7 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT54" t="n">
@@ -11022,42 +11019,42 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11089,12 +11086,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -11128,29 +11125,29 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="O55" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+          <t>Invasive group A streptococcal infection</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -11160,7 +11157,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -11175,7 +11172,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -11210,17 +11207,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+          <t>New Zealand PHF Science monthly invasive group A streptococcal infection notifications.</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11243,7 +11240,7 @@
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT55" t="n">
@@ -11256,42 +11253,42 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11323,12 +11320,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -11353,22 +11350,22 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O56" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="R56" t="n">
-        <v>0.3007258903852361</v>
+        <v>0.3270708149899171</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -11377,7 +11374,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -11402,7 +11399,7 @@
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT56" t="n">
@@ -11415,42 +11412,42 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -11482,12 +11479,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -11512,38 +11509,38 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O57" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Syst. gr. A streptokokksykdom</t>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -11568,7 +11565,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
@@ -11603,17 +11600,17 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -11636,7 +11633,7 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT57" t="n">
@@ -11649,42 +11646,42 @@
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -11716,12 +11713,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -11755,13 +11752,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="O58" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="R58" t="n">
-        <v>0.4485542605576006</v>
+        <v>0.3007258903852361</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -11770,7 +11767,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -11795,7 +11792,7 @@
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="AT58" t="n">
@@ -11808,42 +11805,42 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -11875,12 +11872,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -11914,29 +11911,29 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="O59" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+          <t>Syst. gr. A streptokokksykdom</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -11961,7 +11958,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -11996,17 +11993,17 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12029,7 +12026,7 @@
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="AT59" t="n">
@@ -12042,42 +12039,42 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -12109,12 +12106,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -12139,22 +12136,22 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="O60" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="R60" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.4485542605576006</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -12163,7 +12160,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -12188,7 +12185,7 @@
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT60" t="n">
@@ -12201,42 +12198,42 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -12268,12 +12265,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -12298,38 +12295,38 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="O61" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Syst. gr. A streptokokksykdom</t>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -12354,7 +12351,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
@@ -12389,17 +12386,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12422,7 +12419,7 @@
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT61" t="n">
@@ -12435,40 +12432,433 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA61" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB61" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>2</v>
+      </c>
+      <c r="O62" t="n">
+        <v>2</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.03537951651591013</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV62" t="inlineStr">
+        <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW61" t="inlineStr">
+      <c r="AW62" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
+      <c r="AX62" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY61" t="inlineStr">
+      <c r="AY62" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
+      <c r="AZ62" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA61" t="inlineStr">
+      <c r="BA62" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB61" t="inlineStr">
+      <c r="BB62" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC61" t="inlineStr">
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>2</v>
+      </c>
+      <c r="O63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN63" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV63" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -12590,7 +12980,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -12600,7 +12990,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
@@ -12620,7 +13010,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -12652,7 +13042,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1790</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d157/2026-2029.xlsx
+++ b/diseases/d157/2026-2029.xlsx
@@ -10966,13 +10966,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O54" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R54" t="n">
-        <v>1.134756279883097</v>
+        <v>1.115843675218379</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -11125,10 +11125,10 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O55" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -12145,13 +12145,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="O60" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="R60" t="n">
-        <v>0.4485542605576006</v>
+        <v>0.8321546052476049</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT60" t="n">
@@ -12198,42 +12198,42 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12265,12 +12265,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -12304,29 +12304,29 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="O61" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+          <t>Invasive group A streptococcal infection</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
@@ -12386,17 +12386,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+          <t>New Zealand PHF Science monthly invasive group A streptococcal infection notifications.</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12419,7 +12419,7 @@
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT61" t="n">
@@ -12432,42 +12432,42 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12499,12 +12499,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -12529,22 +12529,22 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="O62" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="R62" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.4485542605576006</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT62" t="n">
@@ -12591,42 +12591,42 @@
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -12658,12 +12658,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -12688,38 +12688,38 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="O63" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Syst. gr. A streptokokksykdom</t>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
@@ -12779,17 +12779,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT63" t="n">
@@ -12825,40 +12825,433 @@
       </c>
       <c r="AV63" t="inlineStr">
         <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>2</v>
+      </c>
+      <c r="O64" t="n">
+        <v>2</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0.03537951651591013</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV64" t="inlineStr">
+        <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW63" t="inlineStr">
+      <c r="AW64" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
+      <c r="AX64" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY63" t="inlineStr">
+      <c r="AY64" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
+      <c r="AZ64" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA63" t="inlineStr">
+      <c r="BA64" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB63" t="inlineStr">
+      <c r="BB64" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC63" t="inlineStr">
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>2</v>
+      </c>
+      <c r="O65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN65" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -12980,7 +13373,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -12990,7 +13383,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
@@ -13010,7 +13403,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -13042,7 +13435,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1883</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d157/2026-2029.xlsx
+++ b/diseases/d157/2026-2029.xlsx
@@ -12931,13 +12931,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O64" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="R64" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.1592078243215956</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -13090,10 +13090,10 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O65" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1926</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d157/2026-2029.xlsx
+++ b/diseases/d157/2026-2029.xlsx
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O52" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R52" t="n">
-        <v>0.3007258903852361</v>
+        <v>0.283036132127281</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -10732,10 +10732,10 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O53" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -12538,13 +12538,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O62" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R62" t="n">
-        <v>0.4485542605576006</v>
+        <v>0.4392093801293172</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -12697,10 +12697,10 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O63" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -12931,13 +12931,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O64" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="R64" t="n">
-        <v>0.1592078243215956</v>
+        <v>0.2476566156113709</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -13090,10 +13090,10 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O65" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1933</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d157/2026-2029.xlsx
+++ b/diseases/d157/2026-2029.xlsx
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12931,13 +12931,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O64" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="R64" t="n">
-        <v>0.2476566156113709</v>
+        <v>0.3361054069011462</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -13090,10 +13090,10 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O65" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1936</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d157/2026-2029.xlsx
+++ b/diseases/d157/2026-2029.xlsx
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O34" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -7201,10 +7201,10 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O35" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8614,10 +8614,10 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O42" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O43" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10183,10 +10183,10 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O50" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -10339,10 +10339,10 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O51" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11713,12 +11713,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -11752,22 +11752,19 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="O58" t="n">
-        <v>17</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0.3007258903852361</v>
+        <v>116</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -11792,7 +11789,7 @@
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="AT58" t="n">
@@ -11805,42 +11802,42 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11872,12 +11869,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -11911,29 +11908,29 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="O59" t="n">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Syst. gr. A streptokokksykdom</t>
+          <t>Group A Streptococcal Disease, Invasive</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -11943,7 +11940,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -11958,7 +11955,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -11993,17 +11990,17 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+          <t>Ontario IDTO current-year preliminary invasive group A streptococcal disease notifications.</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12026,7 +12023,7 @@
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="AT59" t="n">
@@ -12039,42 +12036,42 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12103,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -12145,13 +12142,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O60" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="R60" t="n">
-        <v>0.8321546052476049</v>
+        <v>0.3007258903852361</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -12160,7 +12157,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -12185,7 +12182,7 @@
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="AT60" t="n">
@@ -12198,42 +12195,42 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -12265,12 +12262,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -12304,29 +12301,29 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="O61" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Invasive group A streptococcal infection</t>
+          <t>Syst. gr. A streptokokksykdom</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -12336,7 +12333,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -12351,7 +12348,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
@@ -12386,17 +12383,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly invasive group A streptococcal infection notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12419,7 +12416,7 @@
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="AT61" t="n">
@@ -12432,42 +12429,42 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -12499,12 +12496,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -12538,13 +12535,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O62" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="R62" t="n">
-        <v>0.4392093801293172</v>
+        <v>0.8321546052476049</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -12553,7 +12550,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -12578,7 +12575,7 @@
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT62" t="n">
@@ -12591,42 +12588,42 @@
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12658,12 +12655,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -12697,29 +12694,29 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O63" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+          <t>Invasive group A streptococcal infection</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -12729,7 +12726,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -12744,7 +12741,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
@@ -12779,17 +12776,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+          <t>New Zealand PHF Science monthly invasive group A streptococcal infection notifications.</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -12812,7 +12809,7 @@
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT63" t="n">
@@ -12825,42 +12822,42 @@
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12892,12 +12889,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -12922,22 +12919,22 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="O64" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="R64" t="n">
-        <v>0.3361054069011462</v>
+        <v>0.4392093801293172</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -12946,7 +12943,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -12971,7 +12968,7 @@
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT64" t="n">
@@ -12984,42 +12981,42 @@
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -13051,12 +13048,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -13081,38 +13078,38 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="O65" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Syst. gr. A streptokokksykdom</t>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -13137,7 +13134,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
@@ -13172,17 +13169,17 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13205,7 +13202,7 @@
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT65" t="n">
@@ -13218,40 +13215,1219 @@
       </c>
       <c r="AV65" t="inlineStr">
         <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>19</v>
+      </c>
+      <c r="O66" t="n">
+        <v>19</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.3361054069011462</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV66" t="inlineStr">
+        <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW65" t="inlineStr">
+      <c r="AW66" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
+      <c r="AX66" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY65" t="inlineStr">
+      <c r="AY66" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
+      <c r="AZ66" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA65" t="inlineStr">
+      <c r="BA66" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB65" t="inlineStr">
+      <c r="BB66" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC65" t="inlineStr">
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>19</v>
+      </c>
+      <c r="O67" t="n">
+        <v>19</v>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN67" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV67" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA67" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>30</v>
+      </c>
+      <c r="O68" t="n">
+        <v>30</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0.2803464128485004</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AT68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV68" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA68" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>30</v>
+      </c>
+      <c r="O69" t="n">
+        <v>30</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN69" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP69" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AT69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV69" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA69" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV70" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN71" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -13290,7 +14466,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -13373,7 +14549,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -13383,7 +14559,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -13403,7 +14579,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -13435,7 +14611,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1941</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d157/2026-2029.xlsx
+++ b/diseases/d157/2026-2029.xlsx
@@ -14107,13 +14107,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R70" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -14266,10 +14266,10 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2089</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d157/2026-2029.xlsx
+++ b/diseases/d157/2026-2029.xlsx
@@ -3511,13 +3511,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O16" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5513479452687174</v>
+        <v>0.542003064840434</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O17" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2091</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d157/2026-2029.xlsx
+++ b/diseases/d157/2026-2029.xlsx
@@ -77251,12 +77251,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -77290,13 +77290,13 @@
         </is>
       </c>
       <c r="N396" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="O396" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="R396" t="n">
-        <v>0.2803464128485004</v>
+        <v>1.040193256559506</v>
       </c>
       <c r="S396" t="inlineStr">
         <is>
@@ -77305,7 +77305,7 @@
       </c>
       <c r="U396" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AA396" t="inlineStr">
@@ -77330,7 +77330,7 @@
       </c>
       <c r="AS396" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT396" t="n">
@@ -77343,42 +77343,42 @@
       </c>
       <c r="AV396" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW396" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX396" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY396" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ396" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA396" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB396" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC396" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -77410,12 +77410,12 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -77449,29 +77449,29 @@
         </is>
       </c>
       <c r="N397" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="O397" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="U397" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="V397" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="W397" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X397" t="inlineStr">
         <is>
-          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+          <t>Invasive group A streptococcal infection</t>
         </is>
       </c>
       <c r="Y397" t="inlineStr">
@@ -77481,7 +77481,7 @@
       </c>
       <c r="Z397" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA397" t="inlineStr">
@@ -77496,7 +77496,7 @@
       </c>
       <c r="AC397" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD397" t="inlineStr">
@@ -77531,17 +77531,17 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+          <t>New Zealand PHF Science monthly invasive group A streptococcal infection notifications.</t>
         </is>
       </c>
       <c r="AM397" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN397" t="b">
@@ -77564,7 +77564,7 @@
       </c>
       <c r="AS397" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT397" t="n">
@@ -77577,42 +77577,42 @@
       </c>
       <c r="AV397" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW397" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX397" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY397" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ397" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA397" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB397" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC397" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -77644,12 +77644,12 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>SE-AB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Stockholms, Sweden</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -77683,14 +77683,17 @@
         </is>
       </c>
       <c r="N398" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="O398" t="n">
-        <v>7</v>
+        <v>30</v>
+      </c>
+      <c r="R398" t="n">
+        <v>0.2803464128485004</v>
       </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="U398" t="inlineStr">
@@ -77743,12 +77746,12 @@
       </c>
       <c r="AX398" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY398" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ398" t="inlineStr">
@@ -77763,12 +77766,12 @@
       </c>
       <c r="BB398" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC398" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -77800,12 +77803,12 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>SE-AB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Stockholms, Sweden</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -77839,10 +77842,10 @@
         </is>
       </c>
       <c r="N399" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="O399" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="U399" t="inlineStr">
         <is>
@@ -77886,7 +77889,7 @@
       </c>
       <c r="AC399" t="inlineStr">
         <is>
-          <t>country:SE-AB:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD399" t="inlineStr">
@@ -77977,12 +77980,12 @@
       </c>
       <c r="AX399" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY399" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ399" t="inlineStr">
@@ -77997,12 +78000,12 @@
       </c>
       <c r="BB399" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC399" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -78034,12 +78037,12 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>SE-AC</t>
+          <t>SE-AB</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Västerbottens, Sweden</t>
+          <t>Stockholms, Sweden</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -78073,10 +78076,10 @@
         </is>
       </c>
       <c r="N400" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O400" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S400" t="inlineStr">
         <is>
@@ -78190,12 +78193,12 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>SE-AC</t>
+          <t>SE-AB</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Västerbottens, Sweden</t>
+          <t>Stockholms, Sweden</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -78229,10 +78232,10 @@
         </is>
       </c>
       <c r="N401" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O401" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U401" t="inlineStr">
         <is>
@@ -78276,7 +78279,7 @@
       </c>
       <c r="AC401" t="inlineStr">
         <is>
-          <t>country:SE-AC:national</t>
+          <t>country:SE-AB:national</t>
         </is>
       </c>
       <c r="AD401" t="inlineStr">
@@ -78424,12 +78427,12 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>SE-BD</t>
+          <t>SE-AC</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Norrbottens, Sweden</t>
+          <t>Västerbottens, Sweden</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -78463,10 +78466,10 @@
         </is>
       </c>
       <c r="N402" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O402" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S402" t="inlineStr">
         <is>
@@ -78580,12 +78583,12 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>SE-BD</t>
+          <t>SE-AC</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Norrbottens, Sweden</t>
+          <t>Västerbottens, Sweden</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -78619,10 +78622,10 @@
         </is>
       </c>
       <c r="N403" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O403" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U403" t="inlineStr">
         <is>
@@ -78666,7 +78669,7 @@
       </c>
       <c r="AC403" t="inlineStr">
         <is>
-          <t>country:SE-BD:national</t>
+          <t>country:SE-AC:national</t>
         </is>
       </c>
       <c r="AD403" t="inlineStr">
@@ -78814,12 +78817,12 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>SE-C</t>
+          <t>SE-BD</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Uppsala, Sweden</t>
+          <t>Norrbottens, Sweden</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -78970,12 +78973,12 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>SE-C</t>
+          <t>SE-BD</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Uppsala, Sweden</t>
+          <t>Norrbottens, Sweden</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -79056,7 +79059,7 @@
       </c>
       <c r="AC405" t="inlineStr">
         <is>
-          <t>country:SE-C:national</t>
+          <t>country:SE-BD:national</t>
         </is>
       </c>
       <c r="AD405" t="inlineStr">
@@ -79204,12 +79207,12 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>SE-D</t>
+          <t>SE-C</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Södermanlands, Sweden</t>
+          <t>Uppsala, Sweden</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -79243,10 +79246,10 @@
         </is>
       </c>
       <c r="N406" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O406" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S406" t="inlineStr">
         <is>
@@ -79360,12 +79363,12 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>SE-D</t>
+          <t>SE-C</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>Södermanlands, Sweden</t>
+          <t>Uppsala, Sweden</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -79399,10 +79402,10 @@
         </is>
       </c>
       <c r="N407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U407" t="inlineStr">
         <is>
@@ -79446,7 +79449,7 @@
       </c>
       <c r="AC407" t="inlineStr">
         <is>
-          <t>country:SE-D:national</t>
+          <t>country:SE-C:national</t>
         </is>
       </c>
       <c r="AD407" t="inlineStr">
@@ -79594,12 +79597,12 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>SE-E</t>
+          <t>SE-D</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Östergötlands, Sweden</t>
+          <t>Södermanlands, Sweden</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -79633,10 +79636,10 @@
         </is>
       </c>
       <c r="N408" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O408" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S408" t="inlineStr">
         <is>
@@ -79750,12 +79753,12 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>SE-E</t>
+          <t>SE-D</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Östergötlands, Sweden</t>
+          <t>Södermanlands, Sweden</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -79789,10 +79792,10 @@
         </is>
       </c>
       <c r="N409" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O409" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U409" t="inlineStr">
         <is>
@@ -79836,7 +79839,7 @@
       </c>
       <c r="AC409" t="inlineStr">
         <is>
-          <t>country:SE-E:national</t>
+          <t>country:SE-D:national</t>
         </is>
       </c>
       <c r="AD409" t="inlineStr">
@@ -79984,12 +79987,12 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>SE-F</t>
+          <t>SE-E</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Jönköpings, Sweden</t>
+          <t>Östergötlands, Sweden</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -80023,10 +80026,10 @@
         </is>
       </c>
       <c r="N410" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O410" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S410" t="inlineStr">
         <is>
@@ -80140,12 +80143,12 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>SE-F</t>
+          <t>SE-E</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Jönköpings, Sweden</t>
+          <t>Östergötlands, Sweden</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -80179,10 +80182,10 @@
         </is>
       </c>
       <c r="N411" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O411" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U411" t="inlineStr">
         <is>
@@ -80226,7 +80229,7 @@
       </c>
       <c r="AC411" t="inlineStr">
         <is>
-          <t>country:SE-F:national</t>
+          <t>country:SE-E:national</t>
         </is>
       </c>
       <c r="AD411" t="inlineStr">
@@ -80374,12 +80377,12 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>SE-G</t>
+          <t>SE-F</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Kronobergs, Sweden</t>
+          <t>Jönköpings, Sweden</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -80413,10 +80416,10 @@
         </is>
       </c>
       <c r="N412" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O412" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S412" t="inlineStr">
         <is>
@@ -80530,12 +80533,12 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>SE-G</t>
+          <t>SE-F</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>Kronobergs, Sweden</t>
+          <t>Jönköpings, Sweden</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -80569,10 +80572,10 @@
         </is>
       </c>
       <c r="N413" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O413" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U413" t="inlineStr">
         <is>
@@ -80616,7 +80619,7 @@
       </c>
       <c r="AC413" t="inlineStr">
         <is>
-          <t>country:SE-G:national</t>
+          <t>country:SE-F:national</t>
         </is>
       </c>
       <c r="AD413" t="inlineStr">
@@ -80764,12 +80767,12 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>SE-H</t>
+          <t>SE-G</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Kalmar, Sweden</t>
+          <t>Kronobergs, Sweden</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -80920,12 +80923,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>SE-H</t>
+          <t>SE-G</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Kalmar, Sweden</t>
+          <t>Kronobergs, Sweden</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -81006,7 +81009,7 @@
       </c>
       <c r="AC415" t="inlineStr">
         <is>
-          <t>country:SE-H:national</t>
+          <t>country:SE-G:national</t>
         </is>
       </c>
       <c r="AD415" t="inlineStr">
@@ -81154,12 +81157,12 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>SE-I</t>
+          <t>SE-H</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Gotlands, Sweden</t>
+          <t>Kalmar, Sweden</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -81193,10 +81196,10 @@
         </is>
       </c>
       <c r="N416" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O416" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S416" t="inlineStr">
         <is>
@@ -81310,12 +81313,12 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>SE-I</t>
+          <t>SE-H</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Gotlands, Sweden</t>
+          <t>Kalmar, Sweden</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -81349,10 +81352,10 @@
         </is>
       </c>
       <c r="N417" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O417" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U417" t="inlineStr">
         <is>
@@ -81396,7 +81399,7 @@
       </c>
       <c r="AC417" t="inlineStr">
         <is>
-          <t>country:SE-I:national</t>
+          <t>country:SE-H:national</t>
         </is>
       </c>
       <c r="AD417" t="inlineStr">
@@ -81544,12 +81547,12 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>SE-K</t>
+          <t>SE-I</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Blekinge, Sweden</t>
+          <t>Gotlands, Sweden</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -81583,10 +81586,10 @@
         </is>
       </c>
       <c r="N418" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O418" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S418" t="inlineStr">
         <is>
@@ -81700,12 +81703,12 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>SE-K</t>
+          <t>SE-I</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Blekinge, Sweden</t>
+          <t>Gotlands, Sweden</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -81739,10 +81742,10 @@
         </is>
       </c>
       <c r="N419" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O419" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U419" t="inlineStr">
         <is>
@@ -81786,7 +81789,7 @@
       </c>
       <c r="AC419" t="inlineStr">
         <is>
-          <t>country:SE-K:national</t>
+          <t>country:SE-I:national</t>
         </is>
       </c>
       <c r="AD419" t="inlineStr">
@@ -81934,12 +81937,12 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>SE-M</t>
+          <t>SE-K</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Skåne, Sweden</t>
+          <t>Blekinge, Sweden</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -81973,10 +81976,10 @@
         </is>
       </c>
       <c r="N420" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O420" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S420" t="inlineStr">
         <is>
@@ -82090,12 +82093,12 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>SE-M</t>
+          <t>SE-K</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Skåne, Sweden</t>
+          <t>Blekinge, Sweden</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -82129,10 +82132,10 @@
         </is>
       </c>
       <c r="N421" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O421" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U421" t="inlineStr">
         <is>
@@ -82176,7 +82179,7 @@
       </c>
       <c r="AC421" t="inlineStr">
         <is>
-          <t>country:SE-M:national</t>
+          <t>country:SE-K:national</t>
         </is>
       </c>
       <c r="AD421" t="inlineStr">
@@ -82324,12 +82327,12 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>SE-N</t>
+          <t>SE-M</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Hallands, Sweden</t>
+          <t>Skåne, Sweden</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -82363,10 +82366,10 @@
         </is>
       </c>
       <c r="N422" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O422" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S422" t="inlineStr">
         <is>
@@ -82480,12 +82483,12 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>SE-N</t>
+          <t>SE-M</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Hallands, Sweden</t>
+          <t>Skåne, Sweden</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -82519,10 +82522,10 @@
         </is>
       </c>
       <c r="N423" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O423" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U423" t="inlineStr">
         <is>
@@ -82566,7 +82569,7 @@
       </c>
       <c r="AC423" t="inlineStr">
         <is>
-          <t>country:SE-N:national</t>
+          <t>country:SE-M:national</t>
         </is>
       </c>
       <c r="AD423" t="inlineStr">
@@ -82714,12 +82717,12 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>SE-O</t>
+          <t>SE-N</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Västra Götalands, Sweden</t>
+          <t>Hallands, Sweden</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -82753,10 +82756,10 @@
         </is>
       </c>
       <c r="N424" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O424" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S424" t="inlineStr">
         <is>
@@ -82870,12 +82873,12 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>SE-O</t>
+          <t>SE-N</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>Västra Götalands, Sweden</t>
+          <t>Hallands, Sweden</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -82909,10 +82912,10 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O425" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U425" t="inlineStr">
         <is>
@@ -82956,7 +82959,7 @@
       </c>
       <c r="AC425" t="inlineStr">
         <is>
-          <t>country:SE-O:national</t>
+          <t>country:SE-N:national</t>
         </is>
       </c>
       <c r="AD425" t="inlineStr">
@@ -83104,12 +83107,12 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>SE-S</t>
+          <t>SE-O</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Värmlands, Sweden</t>
+          <t>Västra Götalands, Sweden</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -83143,10 +83146,10 @@
         </is>
       </c>
       <c r="N426" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O426" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S426" t="inlineStr">
         <is>
@@ -83260,12 +83263,12 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>SE-S</t>
+          <t>SE-O</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>Värmlands, Sweden</t>
+          <t>Västra Götalands, Sweden</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -83299,10 +83302,10 @@
         </is>
       </c>
       <c r="N427" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O427" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U427" t="inlineStr">
         <is>
@@ -83346,7 +83349,7 @@
       </c>
       <c r="AC427" t="inlineStr">
         <is>
-          <t>country:SE-S:national</t>
+          <t>country:SE-O:national</t>
         </is>
       </c>
       <c r="AD427" t="inlineStr">
@@ -83494,12 +83497,12 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>SE-T</t>
+          <t>SE-S</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Örebro, Sweden</t>
+          <t>Värmlands, Sweden</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -83650,12 +83653,12 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>SE-T</t>
+          <t>SE-S</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>Örebro, Sweden</t>
+          <t>Värmlands, Sweden</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -83736,7 +83739,7 @@
       </c>
       <c r="AC429" t="inlineStr">
         <is>
-          <t>country:SE-T:national</t>
+          <t>country:SE-S:national</t>
         </is>
       </c>
       <c r="AD429" t="inlineStr">
@@ -83884,12 +83887,12 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>SE-U</t>
+          <t>SE-T</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>Västmanlands, Sweden</t>
+          <t>Örebro, Sweden</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -84040,12 +84043,12 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>SE-U</t>
+          <t>SE-T</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>Västmanlands, Sweden</t>
+          <t>Örebro, Sweden</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -84126,7 +84129,7 @@
       </c>
       <c r="AC431" t="inlineStr">
         <is>
-          <t>country:SE-U:national</t>
+          <t>country:SE-T:national</t>
         </is>
       </c>
       <c r="AD431" t="inlineStr">
@@ -84274,12 +84277,12 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>SE-W</t>
+          <t>SE-U</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>Dalarnas, Sweden</t>
+          <t>Västmanlands, Sweden</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -84430,12 +84433,12 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>SE-W</t>
+          <t>SE-U</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>Dalarnas, Sweden</t>
+          <t>Västmanlands, Sweden</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -84516,7 +84519,7 @@
       </c>
       <c r="AC433" t="inlineStr">
         <is>
-          <t>country:SE-W:national</t>
+          <t>country:SE-U:national</t>
         </is>
       </c>
       <c r="AD433" t="inlineStr">
@@ -84664,12 +84667,12 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>SE-X</t>
+          <t>SE-W</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Gävleborgs, Sweden</t>
+          <t>Dalarnas, Sweden</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -84703,10 +84706,10 @@
         </is>
       </c>
       <c r="N434" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O434" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S434" t="inlineStr">
         <is>
@@ -84820,12 +84823,12 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>SE-X</t>
+          <t>SE-W</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Gävleborgs, Sweden</t>
+          <t>Dalarnas, Sweden</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -84859,10 +84862,10 @@
         </is>
       </c>
       <c r="N435" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O435" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U435" t="inlineStr">
         <is>
@@ -84906,7 +84909,7 @@
       </c>
       <c r="AC435" t="inlineStr">
         <is>
-          <t>country:SE-X:national</t>
+          <t>country:SE-W:national</t>
         </is>
       </c>
       <c r="AD435" t="inlineStr">
@@ -85054,12 +85057,12 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>SE-Y</t>
+          <t>SE-X</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Västernorrlands, Sweden</t>
+          <t>Gävleborgs, Sweden</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -85093,10 +85096,10 @@
         </is>
       </c>
       <c r="N436" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O436" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S436" t="inlineStr">
         <is>
@@ -85210,12 +85213,12 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>SE-Y</t>
+          <t>SE-X</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Västernorrlands, Sweden</t>
+          <t>Gävleborgs, Sweden</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -85249,10 +85252,10 @@
         </is>
       </c>
       <c r="N437" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O437" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U437" t="inlineStr">
         <is>
@@ -85296,7 +85299,7 @@
       </c>
       <c r="AC437" t="inlineStr">
         <is>
-          <t>country:SE-Y:national</t>
+          <t>country:SE-X:national</t>
         </is>
       </c>
       <c r="AD437" t="inlineStr">
@@ -85444,12 +85447,12 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>SE-Z</t>
+          <t>SE-Y</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Jämtlands, Sweden</t>
+          <t>Västernorrlands, Sweden</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -85600,12 +85603,12 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>SE-Z</t>
+          <t>SE-Y</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Jämtlands, Sweden</t>
+          <t>Västernorrlands, Sweden</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -85686,7 +85689,7 @@
       </c>
       <c r="AC439" t="inlineStr">
         <is>
-          <t>country:SE-Z:national</t>
+          <t>country:SE-Y:national</t>
         </is>
       </c>
       <c r="AD439" t="inlineStr">
@@ -85834,12 +85837,12 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE-Z</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Jämtlands, Sweden</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -85864,31 +85867,28 @@
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N440" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O440" t="n">
-        <v>3</v>
-      </c>
-      <c r="R440" t="n">
-        <v>0.05306927477386519</v>
+        <v>0</v>
       </c>
       <c r="S440" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U440" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AA440" t="inlineStr">
@@ -85913,7 +85913,7 @@
       </c>
       <c r="AS440" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT440" t="n">
@@ -85926,42 +85926,42 @@
       </c>
       <c r="AV440" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW440" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX440" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/</t>
         </is>
       </c>
       <c r="AY440" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ440" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA440" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB440" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/</t>
         </is>
       </c>
       <c r="BC440" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -85993,12 +85993,12 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE-Z</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Jämtlands, Sweden</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -86023,38 +86023,38 @@
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N441" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O441" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U441" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="V441" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="W441" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X441" t="inlineStr">
         <is>
-          <t>Syst. gr. A streptokokksykdom</t>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
         </is>
       </c>
       <c r="Y441" t="inlineStr">
@@ -86079,7 +86079,7 @@
       </c>
       <c r="AC441" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:SE-Z:national</t>
         </is>
       </c>
       <c r="AD441" t="inlineStr">
@@ -86114,17 +86114,17 @@
       </c>
       <c r="AJ441" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK441" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
         </is>
       </c>
       <c r="AM441" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN441" t="b">
@@ -86147,7 +86147,7 @@
       </c>
       <c r="AS441" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT441" t="n">
@@ -86160,40 +86160,433 @@
       </c>
       <c r="AV441" t="inlineStr">
         <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW441" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX441" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/</t>
+        </is>
+      </c>
+      <c r="AY441" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ441" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA441" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB441" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/</t>
+        </is>
+      </c>
+      <c r="BC441" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N442" t="n">
+        <v>3</v>
+      </c>
+      <c r="O442" t="n">
+        <v>3</v>
+      </c>
+      <c r="R442" t="n">
+        <v>0.05306927477386519</v>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA442" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO442" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP442" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ442" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS442" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT442" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU442" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV442" t="inlineStr">
+        <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW441" t="inlineStr">
+      <c r="AW442" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX441" t="inlineStr">
+      <c r="AX442" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY441" t="inlineStr">
+      <c r="AY442" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ441" t="inlineStr">
+      <c r="AZ442" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA441" t="inlineStr">
+      <c r="BA442" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB441" t="inlineStr">
+      <c r="BB442" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC441" t="inlineStr">
+      <c r="BC442" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N443" t="n">
+        <v>3</v>
+      </c>
+      <c r="O443" t="n">
+        <v>3</v>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V443" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W443" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X443" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y443" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z443" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA443" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB443" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC443" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD443" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE443" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF443" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG443" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH443" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI443" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ443" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK443" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM443" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN443" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO443" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP443" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ443" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS443" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT443" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU443" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV443" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW443" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX443" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY443" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ443" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA443" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB443" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC443" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -86315,7 +86708,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10">
@@ -86325,7 +86718,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="11">
@@ -86345,7 +86738,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -86377,7 +86770,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2508</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="16">
